--- a/members.xlsx
+++ b/members.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dghy1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D6D802-A2C6-4DBC-8581-5731BBA13F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AECCCC-4C03-4FD7-AEF5-E31BE07BE70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="個別" sheetId="1" r:id="rId1"/>
+    <sheet name="共通" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -98,29 +99,311 @@
     <t>男</t>
   </si>
   <si>
-    <t>東京都中央区銀座1-2-3</t>
-  </si>
-  <si>
-    <t>011-123-4567</t>
-  </si>
-  <si>
-    <t>山本 久子</t>
-  </si>
-  <si>
-    <t>ヤマモト ヒサコ</t>
-  </si>
-  <si>
     <t>女</t>
   </si>
   <si>
-    <t>東京都中央区日本橋3-4-5</t>
-  </si>
-  <si>
     <t xml:space="preserve">                     </t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>03-2345-6789</t>
+    <t>東京都中央区青葉町 3-5-7</t>
+  </si>
+  <si>
+    <t>東京都中央区東通り 1-2-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-2345-6798</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-9123-4567</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連絡先氏名</t>
+    <rPh sb="0" eb="3">
+      <t>レンラクサキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提出代行者　名称</t>
+    <rPh sb="0" eb="2">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ダイコウシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提出代行者　住所</t>
+    <rPh sb="0" eb="2">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ダイコウシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジュウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主治医の氏名</t>
+    <rPh sb="0" eb="3">
+      <t>シュジイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>医療機関名</t>
+    <rPh sb="0" eb="2">
+      <t>イリョウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キカンメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提出代行者　郵便番号</t>
+    <rPh sb="0" eb="2">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ダイコウシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ユウビン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提出代行者　電話番号</t>
+    <rPh sb="0" eb="2">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ダイコウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>所在地　郵便番号</t>
+    <rPh sb="0" eb="3">
+      <t>ショザイチ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>所在地　住所</t>
+    <rPh sb="0" eb="3">
+      <t>ショザイチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジュウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>所在地　電話番号</t>
+    <rPh sb="0" eb="3">
+      <t>ショザイチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被保険者番号</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>ホケンシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要介護状態区分</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウカイゴ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要介護3</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウカイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要支援1</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウシエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山田 太郎</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-5910-8821</t>
+  </si>
+  <si>
+    <t>104-8721</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都中央区銀河橋1-3-9 銀河橋センタービル3F</t>
+    <rPh sb="6" eb="9">
+      <t>ギンガバシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-5910-7703</t>
+  </si>
+  <si>
+    <t>井上 直樹</t>
+  </si>
+  <si>
+    <t>すこやかメディカルセンター</t>
+  </si>
+  <si>
+    <t>104-8739</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都中央区東光川5-6-3</t>
+    <rPh sb="0" eb="3">
+      <t>トウキョウト</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>チュウオウク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-6802-8647</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>株式会社なごみ福祉サービス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>介護保険施設の名称等</t>
+    <rPh sb="0" eb="2">
+      <t>カイゴ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シセツ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>メイショウトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>介護保険施設の所在地</t>
+    <rPh sb="0" eb="2">
+      <t>カイゴ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シセツ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ショザイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀河橋なごみケアホーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都中央区</t>
+    <rPh sb="0" eb="3">
+      <t>トウキョウト</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>チュウオウク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モトムラ トモコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本村 朋子</t>
+    <rPh sb="0" eb="2">
+      <t>モトムラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トモコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -197,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -207,6 +490,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -487,17 +773,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="24.75" customWidth="1"/>
     <col min="3" max="3" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="21.75" customWidth="1"/>
+    <col min="8" max="10" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -522,8 +808,14 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -531,10 +823,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="3">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3">
         <v>15</v>
@@ -542,19 +834,25 @@
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1310204536</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3">
         <v>1938</v>
@@ -563,27 +861,141 @@
         <v>11</v>
       </c>
       <c r="E3" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>18</v>
+      <c r="I3" s="5">
+        <v>1310981267</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2749E1FA-0AAF-43E7-BEAD-9F7BC6F39B3D}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="15.375" customWidth="1"/>
+    <col min="3" max="3" width="23.875" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="27.75" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="43.625" customWidth="1"/>
+    <col min="8" max="8" width="21.875" customWidth="1"/>
+    <col min="9" max="9" width="16.25" customWidth="1"/>
+    <col min="10" max="10" width="27.5" customWidth="1"/>
+    <col min="11" max="11" width="17.875" customWidth="1"/>
+    <col min="12" max="12" width="24.625" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
         <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/members.xlsx
+++ b/members.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dghy1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AECCCC-4C03-4FD7-AEF5-E31BE07BE70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13580749-1585-4B35-97CB-A46D9EDE86B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="17280" windowHeight="10665" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="個別" sheetId="1" r:id="rId1"/>
@@ -302,13 +302,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>東京都中央区銀河橋1-3-9 銀河橋センタービル3F</t>
-    <rPh sb="6" eb="9">
-      <t>ギンガバシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>03-5910-7703</t>
   </si>
   <si>
@@ -378,10 +371,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>銀河橋なごみケアホーム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>東京都中央区</t>
     <rPh sb="0" eb="3">
       <t>トウキョウト</t>
@@ -396,12 +385,32 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>本村 朋子</t>
+    <t>本村 和子</t>
     <rPh sb="0" eb="2">
       <t>モトムラ</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>トモコ</t>
+      <t>カズコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高浜橋なごみケアホーム</t>
+    <rPh sb="0" eb="2">
+      <t>タカハマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>バシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都中央区高浜橋1-3-9 銀河橋センタービル3F</t>
+    <rPh sb="6" eb="8">
+      <t>タカハマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>バシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -849,10 +858,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3">
         <v>1938</v>
@@ -924,10 +933,10 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" t="s">
-        <v>43</v>
       </c>
       <c r="E1" t="s">
         <v>18</v>
@@ -965,37 +974,37 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>33</v>
       </c>
       <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
